--- a/Stock_OneClick/history/scan_result_20260601_135720.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_135720.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q189"/>
+  <dimension ref="A1:Q188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -665,24 +665,6 @@
       <c r="J3" t="n">
         <v>185.67</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-01; 相对D0=2.30%; 本次触发=2026-05-22(正式买入), 2026-05-27(正式买入 | 预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -734,24 +716,12 @@
       <c r="J4" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-01; 相对D0=-7.16%; 本次触发=2026-05-22(预警买入), 2026-05-26(预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -803,24 +773,12 @@
       <c r="J5" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-01; 相对D0=-2.56%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入), 2026-05-29(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -872,27 +830,15 @@
       <c r="J6" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>D0=294.07; 最新=2026-06-01; 相对D0=-9.65%; 本次触发=2026-05-22(第一买入点), 2026-05-29(正式买入); 历史重复1次; 重复日期=2026-05-29</t>
+          <t>D0=294.07; 最新=2026-06-01; 相对D0=-9.65%; 本次触发=2026-05-22(第一观察点), 2026-05-29(正式买入); 历史重复1次; 重复日期=2026-05-29</t>
         </is>
       </c>
     </row>
@@ -941,24 +887,12 @@
       <c r="J7" s="5" t="n">
         <v>54.5</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-01; 相对D0=17.13%; 本次触发=2026-05-22(正式买入)</t>
@@ -1010,24 +944,6 @@
       <c r="J8" t="n">
         <v>16.62</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-01; 相对D0=3.10%; 本次触发=2026-05-22(预警买入), 2026-05-27(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
@@ -1079,24 +995,12 @@
       <c r="J9" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-01; 相对D0=16.40%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-28(预警买入), 2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1148,24 +1052,12 @@
       <c r="J10" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-01; 相对D0=-1.10%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入), 2026-05-29(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -1217,24 +1109,12 @@
       <c r="J11" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-01; 相对D0=0.33%; 本次触发=2026-05-22(正式买入)</t>
@@ -1286,24 +1166,6 @@
       <c r="J12" t="n">
         <v>136.62</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-01; 相对D0=-3.26%; 本次触发=2026-05-22(预警买入), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1355,24 +1217,6 @@
       <c r="J13" t="n">
         <v>400.08</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-01; 相对D0=2.23%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1424,24 +1268,6 @@
       <c r="J14" t="n">
         <v>950.54</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-01; 相对D0=-8.49%; 本次触发=2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1493,24 +1319,6 @@
       <c r="J15" t="n">
         <v>50.55</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-01; 相对D0=-0.22%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -1562,27 +1370,15 @@
       <c r="J16" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1631,24 +1427,12 @@
       <c r="J17" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-01; 相对D0=23.84%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-05-29(预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -1700,24 +1484,12 @@
       <c r="J18" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-01; 相对D0=-1.60%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1769,27 +1541,9 @@
       <c r="J19" t="n">
         <v>23.33</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 本次触发=2026-05-22(正式买入), 2026-05-26(第一买入点); 历史重复1次; 重复日期=2026-05-26</t>
+          <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 本次触发=2026-05-22(正式买入), 2026-05-26(第一观察点); 历史重复1次; 重复日期=2026-05-26</t>
         </is>
       </c>
     </row>
@@ -1838,27 +1592,15 @@
       <c r="J20" s="5" t="n">
         <v>29.7</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>D0=26.73; 最新=2026-06-01; 相对D0=11.11%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=26.73; 最新=2026-06-01; 相对D0=11.11%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1907,27 +1649,9 @@
       <c r="J21" t="n">
         <v>129.47</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>D0=137.65; 最新=2026-06-01; 相对D0=-5.94%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=137.65; 最新=2026-06-01; 相对D0=-5.94%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1976,24 +1700,6 @@
       <c r="J22" t="n">
         <v>251.49</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-01; 相对D0=8.40%; 本次触发=2026-05-22(正式买入)</t>
@@ -2045,24 +1751,6 @@
       <c r="J23" t="n">
         <v>145.02</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-01; 相对D0=11.13%; 本次触发=2026-05-22(正式买入 | 预警买入)</t>
@@ -2114,24 +1802,12 @@
       <c r="J24" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-01; 相对D0=-2.49%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入 | 预警买入), 2026-05-27(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -2183,24 +1859,6 @@
       <c r="J25" t="n">
         <v>58.92</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-01; 相对D0=0.19%; 本次触发=2026-05-22(预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -2252,24 +1910,6 @@
       <c r="J26" t="n">
         <v>55.98</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-01; 相对D0=1.89%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -2321,24 +1961,6 @@
       <c r="J27" t="n">
         <v>83.78</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-01; 相对D0=2.47%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -2390,27 +2012,15 @@
       <c r="J28" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 第一买入点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
+          <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 第一观察点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2459,24 +2069,12 @@
       <c r="J29" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-01; 相对D0=-2.38%; 本次触发=2026-05-22(预警买入)</t>
@@ -2528,24 +2126,12 @@
       <c r="J30" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-01; 相对D0=4.38%; 本次触发=2026-05-22(预警买入), 2026-05-26(预警买入), 2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2597,24 +2183,6 @@
       <c r="J31" t="n">
         <v>379.86</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-01; 相对D0=-2.22%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(预警买入); 历史重复1次; 重复日期=2026-05-27</t>
@@ -2666,27 +2234,9 @@
       <c r="J32" t="n">
         <v>154.76</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>D0=156.27; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=156.27; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -2735,24 +2285,6 @@
       <c r="J33" t="n">
         <v>50.92</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-01; 相对D0=1.25%; 本次触发=2026-05-22(预警买入), 2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -2804,24 +2336,12 @@
       <c r="J34" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-26(正式买入 | 预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -2873,24 +2393,6 @@
       <c r="J35" t="n">
         <v>459.97</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-01; 相对D0=9.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -2942,24 +2444,6 @@
       <c r="J36" t="n">
         <v>91.22</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-01; 相对D0=5.47%; 本次触发=2026-05-26(预警买入)</t>
@@ -3011,24 +2495,12 @@
       <c r="J37" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-01; 相对D0=-7.82%; 本次触发=2026-05-26(预警买入)</t>
@@ -3080,24 +2552,12 @@
       <c r="J38" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-01; 相对D0=-6.66%; 本次触发=2026-05-26(正式买入)</t>
@@ -3149,24 +2609,12 @@
       <c r="J39" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-01; 相对D0=4.09%; 本次触发=2026-05-26(预警买入), 2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -3218,24 +2666,6 @@
       <c r="J40" t="n">
         <v>124.82</v>
       </c>
-      <c r="K40" t="n">
-        <v/>
-      </c>
-      <c r="L40" t="n">
-        <v/>
-      </c>
-      <c r="M40" t="n">
-        <v/>
-      </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
-      <c r="O40" t="n">
-        <v/>
-      </c>
-      <c r="P40" t="n">
-        <v/>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-01; 相对D0=17.88%; 本次触发=2026-05-26(预警买入), 2026-05-28(预警买入), 2026-05-29(正式买入); 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3287,24 +2717,12 @@
       <c r="J41" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-01; 相对D0=-3.78%; 本次触发=2026-05-26(正式买入)</t>
@@ -3356,24 +2774,6 @@
       <c r="J42" t="n">
         <v>400.08</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-01; 相对D0=-0.76%; 本次触发=2026-05-26(正式买入)</t>
@@ -3425,24 +2825,6 @@
       <c r="J43" t="n">
         <v>950.54</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-01; 相对D0=-11.20%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -3494,24 +2876,12 @@
       <c r="J44" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-01; 相对D0=-3.22%; 本次触发=2026-05-26(正式买入 | 预警买入), 2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -3563,24 +2933,12 @@
       <c r="J45" s="5" t="n">
         <v>69.86</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-01; 相对D0=0.33%; 本次触发=2026-05-26(预警买入)</t>
@@ -3632,24 +2990,12 @@
       <c r="J46" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-01; 相对D0=-1.94%; 本次触发=2026-05-26(正式买入)</t>
@@ -3701,27 +3047,9 @@
       <c r="J47" t="n">
         <v>23.33</v>
       </c>
-      <c r="K47" t="n">
-        <v/>
-      </c>
-      <c r="L47" t="n">
-        <v/>
-      </c>
-      <c r="M47" t="n">
-        <v/>
-      </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
-      <c r="O47" t="n">
-        <v/>
-      </c>
-      <c r="P47" t="n">
-        <v/>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>D0=22.62; 最新=2026-06-01; 相对D0=3.14%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=22.62; 最新=2026-06-01; 相对D0=3.14%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -3770,24 +3098,12 @@
       <c r="J48" s="5" t="n">
         <v>131.85</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-01; 相对D0=-2.05%; 本次触发=2026-05-26(正式买入), 2026-05-28(正式买入); 历史重复1次; 重复日期=2026-05-28</t>
@@ -3839,27 +3155,15 @@
       <c r="J49" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-05-26(第一买入点), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
+          <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-05-26(第一观察点), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3908,24 +3212,12 @@
       <c r="J50" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-01; 相对D0=-6.73%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -3977,24 +3269,6 @@
       <c r="J51" t="n">
         <v>55.98</v>
       </c>
-      <c r="K51" t="n">
-        <v/>
-      </c>
-      <c r="L51" t="n">
-        <v/>
-      </c>
-      <c r="M51" t="n">
-        <v/>
-      </c>
-      <c r="N51" t="n">
-        <v/>
-      </c>
-      <c r="O51" t="n">
-        <v/>
-      </c>
-      <c r="P51" t="n">
-        <v/>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-01; 相对D0=-0.59%; 本次触发=2026-05-26(正式买入)</t>
@@ -4046,24 +3320,6 @@
       <c r="J52" t="n">
         <v>108.96</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
-      <c r="L52" t="n">
-        <v/>
-      </c>
-      <c r="M52" t="n">
-        <v/>
-      </c>
-      <c r="N52" t="n">
-        <v/>
-      </c>
-      <c r="O52" t="n">
-        <v/>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-01; 相对D0=1.89%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -4115,27 +3371,15 @@
       <c r="J53" s="5" t="n">
         <v>12.89</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -4184,27 +3428,9 @@
       <c r="J54" t="n">
         <v>18.58</v>
       </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="n">
-        <v/>
-      </c>
-      <c r="N54" t="n">
-        <v/>
-      </c>
-      <c r="O54" t="n">
-        <v/>
-      </c>
-      <c r="P54" t="n">
-        <v/>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>D0=15.98; 最新=2026-06-01; 相对D0=16.27%; 本次触发=2026-05-26(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=15.98; 最新=2026-06-01; 相对D0=16.27%; 本次触发=2026-05-26(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -4253,24 +3479,6 @@
       <c r="J55" t="n">
         <v>83.78</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-01; 相对D0=-1.02%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -4322,24 +3530,12 @@
       <c r="J56" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-01; 相对D0=0.59%; 本次触发=2026-05-26(预警买入)</t>
@@ -4391,24 +3587,12 @@
       <c r="J57" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-01; 相对D0=-4.24%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -4460,24 +3644,6 @@
       <c r="J58" t="n">
         <v>323.39</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-01; 相对D0=-0.16%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -4529,24 +3695,6 @@
       <c r="J59" t="n">
         <v>50.92</v>
       </c>
-      <c r="K59" t="n">
-        <v/>
-      </c>
-      <c r="L59" t="n">
-        <v/>
-      </c>
-      <c r="M59" t="n">
-        <v/>
-      </c>
-      <c r="N59" t="n">
-        <v/>
-      </c>
-      <c r="O59" t="n">
-        <v/>
-      </c>
-      <c r="P59" t="n">
-        <v/>
-      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-01; 相对D0=-0.14%; 本次触发=2026-05-26(正式买入)</t>
@@ -4598,24 +3746,6 @@
       <c r="J60" t="n">
         <v>185.67</v>
       </c>
-      <c r="K60" t="n">
-        <v/>
-      </c>
-      <c r="L60" t="n">
-        <v/>
-      </c>
-      <c r="M60" t="n">
-        <v/>
-      </c>
-      <c r="N60" t="n">
-        <v/>
-      </c>
-      <c r="O60" t="n">
-        <v/>
-      </c>
-      <c r="P60" t="n">
-        <v/>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-01; 相对D0=3.25%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -4667,24 +3797,12 @@
       <c r="J61" s="5" t="n">
         <v>261.26</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-01; 相对D0=-3.90%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -4736,24 +3854,6 @@
       <c r="J62" t="n">
         <v>16.62</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-01; 相对D0=0.97%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -4805,27 +3905,9 @@
       <c r="J63" t="n">
         <v>27.76</v>
       </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
-      <c r="L63" t="n">
-        <v/>
-      </c>
-      <c r="M63" t="n">
-        <v/>
-      </c>
-      <c r="N63" t="n">
-        <v/>
-      </c>
-      <c r="O63" t="n">
-        <v/>
-      </c>
-      <c r="P63" t="n">
-        <v/>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>D0=25.20; 最新=2026-06-01; 相对D0=10.16%; 本次触发=2026-05-27(正式买入 | 第一买入点)</t>
+          <t>D0=25.20; 最新=2026-06-01; 相对D0=10.16%; 本次触发=2026-05-27(正式买入 | 第一观察点)</t>
         </is>
       </c>
     </row>
@@ -4874,24 +3956,6 @@
       <c r="J64" t="n">
         <v>90.73</v>
       </c>
-      <c r="K64" t="n">
-        <v/>
-      </c>
-      <c r="L64" t="n">
-        <v/>
-      </c>
-      <c r="M64" t="n">
-        <v/>
-      </c>
-      <c r="N64" t="n">
-        <v/>
-      </c>
-      <c r="O64" t="n">
-        <v/>
-      </c>
-      <c r="P64" t="n">
-        <v/>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-01; 相对D0=19.02%; 本次触发=2026-05-27(正式买入 | 预警买入), 2026-05-28(二进宫买入点); 历史重复1次; 重复日期=2026-05-28</t>
@@ -4943,24 +4007,6 @@
       <c r="J65" t="n">
         <v>50.55</v>
       </c>
-      <c r="K65" t="n">
-        <v/>
-      </c>
-      <c r="L65" t="n">
-        <v/>
-      </c>
-      <c r="M65" t="n">
-        <v/>
-      </c>
-      <c r="N65" t="n">
-        <v/>
-      </c>
-      <c r="O65" t="n">
-        <v/>
-      </c>
-      <c r="P65" t="n">
-        <v/>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-01; 相对D0=0.22%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -5012,24 +4058,12 @@
       <c r="J66" s="5" t="n">
         <v>135.86</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-01; 相对D0=33.04%; 本次触发=2026-05-27(预警买入)</t>
@@ -5081,24 +4115,12 @@
       <c r="J67" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-01; 相对D0=-4.19%; 本次触发=2026-05-27(预警买入)</t>
@@ -5150,24 +4172,6 @@
       <c r="J68" t="n">
         <v>248.15</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-01; 相对D0=29.95%; 本次触发=2026-05-27(预警买入)</t>
@@ -5219,27 +4223,15 @@
       <c r="J69" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>D0=89.07; 最新=2026-06-01; 相对D0=30.18%; 本次触发=2026-05-27(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=89.07; 最新=2026-06-01; 相对D0=30.18%; 本次触发=2026-05-27(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -5288,24 +4280,6 @@
       <c r="J70" t="n">
         <v>379.86</v>
       </c>
-      <c r="K70" t="n">
-        <v/>
-      </c>
-      <c r="L70" t="n">
-        <v/>
-      </c>
-      <c r="M70" t="n">
-        <v/>
-      </c>
-      <c r="N70" t="n">
-        <v/>
-      </c>
-      <c r="O70" t="n">
-        <v/>
-      </c>
-      <c r="P70" t="n">
-        <v/>
-      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-01; 相对D0=-1.08%; 本次触发=2026-05-27(预警买入)</t>
@@ -5357,24 +4331,6 @@
       <c r="J71" t="n">
         <v>273.51</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-01; 相对D0=-5.69%; 本次触发=2026-05-28(预警买入)</t>
@@ -5426,24 +4382,12 @@
       <c r="J72" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
       <c r="Q72" s="5" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-01; 相对D0=1.77%; 本次触发=2026-05-28(正式买入)</t>
@@ -5495,24 +4439,6 @@
       <c r="J73" t="n">
         <v>94.15000000000001</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-01; 相对D0=12.51%; 本次触发=2026-05-28(预警买入)</t>
@@ -5564,24 +4490,12 @@
       <c r="J74" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
       <c r="Q74" s="5" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-01; 相对D0=18.98%; 本次触发=2026-05-28(预警买入)</t>
@@ -5633,24 +4547,6 @@
       <c r="J75" t="n">
         <v>782.17</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-01; 相对D0=16.57%; 本次触发=2026-05-28(预警买入)</t>
@@ -5702,24 +4598,6 @@
       <c r="J76" t="n">
         <v>124.82</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-01; 相对D0=16.81%; 本次触发=2026-05-28(预警买入)</t>
@@ -5771,24 +4649,6 @@
       <c r="J77" t="n">
         <v>64.61</v>
       </c>
-      <c r="K77" t="n">
-        <v/>
-      </c>
-      <c r="L77" t="n">
-        <v/>
-      </c>
-      <c r="M77" t="n">
-        <v/>
-      </c>
-      <c r="N77" t="n">
-        <v/>
-      </c>
-      <c r="O77" t="n">
-        <v/>
-      </c>
-      <c r="P77" t="n">
-        <v/>
-      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-01; 相对D0=-4.11%; 本次触发=2026-05-28(预警买入)</t>
@@ -5840,24 +4700,6 @@
       <c r="J78" t="n">
         <v>147.14</v>
       </c>
-      <c r="K78" t="n">
-        <v/>
-      </c>
-      <c r="L78" t="n">
-        <v/>
-      </c>
-      <c r="M78" t="n">
-        <v/>
-      </c>
-      <c r="N78" t="n">
-        <v/>
-      </c>
-      <c r="O78" t="n">
-        <v/>
-      </c>
-      <c r="P78" t="n">
-        <v/>
-      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-01; 相对D0=13.45%; 本次触发=2026-05-28(预警买入)</t>
@@ -5909,24 +4751,12 @@
       <c r="J79" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-01; 相对D0=-3.53%; 本次触发=2026-05-28(正式买入)</t>
@@ -5978,24 +4808,6 @@
       <c r="J80" t="n">
         <v>90.73</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-01; 相对D0=6.94%; 本次触发=2026-05-28(二进宫买入点)</t>
@@ -6047,24 +4859,12 @@
       <c r="J81" s="5" t="n">
         <v>107.7</v>
       </c>
-      <c r="K81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P81" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="n"/>
+      <c r="O81" s="5" t="n"/>
+      <c r="P81" s="5" t="n"/>
       <c r="Q81" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-01; 相对D0=12.56%; 本次触发=2026-05-28(预警买入)</t>
@@ -6116,24 +4916,12 @@
       <c r="J82" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
       <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-01; 相对D0=1.91%; 本次触发=2026-05-28(正式买入 | 预警买入)</t>
@@ -6185,24 +4973,12 @@
       <c r="J83" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-01; 相对D0=24.01%; 本次触发=2026-05-28(正式买入 | 预警买入)</t>
@@ -6254,24 +5030,12 @@
       <c r="J84" s="5" t="n">
         <v>460.52</v>
       </c>
-      <c r="K84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
       <c r="Q84" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-01; 相对D0=7.85%; 本次触发=2026-05-28(正式买入 | 预警买入)</t>
@@ -6323,24 +5087,6 @@
       <c r="J85" t="n">
         <v>264.51</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-01; 相对D0=16.86%; 本次触发=2026-05-28(预警买入)</t>
@@ -6392,24 +5138,12 @@
       <c r="J86" s="5" t="n">
         <v>131.85</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-01; 相对D0=-1.10%; 本次触发=2026-05-28(正式买入)</t>
@@ -6461,24 +5195,6 @@
       <c r="J87" t="n">
         <v>139.79</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-01; 相对D0=47.58%; 本次触发=2026-05-28(预警买入)</t>
@@ -6530,24 +5246,6 @@
       <c r="J88" t="n">
         <v>300.48</v>
       </c>
-      <c r="K88" t="n">
-        <v/>
-      </c>
-      <c r="L88" t="n">
-        <v/>
-      </c>
-      <c r="M88" t="n">
-        <v/>
-      </c>
-      <c r="N88" t="n">
-        <v/>
-      </c>
-      <c r="O88" t="n">
-        <v/>
-      </c>
-      <c r="P88" t="n">
-        <v/>
-      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-01; 相对D0=16.57%; 本次触发=2026-05-28(预警买入)</t>
@@ -6599,24 +5297,12 @@
       <c r="J89" s="5" t="n">
         <v>160.65</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-01; 相对D0=12.08%; 本次触发=2026-05-28(二进宫买入点 | 正式买入 | 预警买入)</t>
@@ -6668,27 +5354,15 @@
       <c r="J90" s="5" t="n">
         <v>274.03</v>
       </c>
-      <c r="K90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="inlineStr">
         <is>
-          <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%; 本次触发=2026-05-29(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%; 本次触发=2026-05-29(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -6737,24 +5411,12 @@
       <c r="J91" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P91" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%; 本次触发=2026-05-29(预警买入)</t>
@@ -6806,24 +5468,12 @@
       <c r="J92" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-01; 相对D0=-7.66%; 本次触发=2026-05-29(正式买入)</t>
@@ -6875,24 +5525,6 @@
       <c r="J93" t="n">
         <v>182.61</v>
       </c>
-      <c r="K93" t="n">
-        <v/>
-      </c>
-      <c r="L93" t="n">
-        <v/>
-      </c>
-      <c r="M93" t="n">
-        <v/>
-      </c>
-      <c r="N93" t="n">
-        <v/>
-      </c>
-      <c r="O93" t="n">
-        <v/>
-      </c>
-      <c r="P93" t="n">
-        <v/>
-      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-01; 相对D0=-3.40%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -6944,24 +5576,12 @@
       <c r="J94" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P94" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="n"/>
+      <c r="M94" s="5" t="n"/>
+      <c r="N94" s="5" t="n"/>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="5" t="n"/>
       <c r="Q94" s="5" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-01; 相对D0=9.68%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -7013,24 +5633,6 @@
       <c r="J95" t="n">
         <v>124.82</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-01; 相对D0=13.96%; 本次触发=2026-05-29(正式买入)</t>
@@ -7082,24 +5684,12 @@
       <c r="J96" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-01; 相对D0=-1.71%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -7151,24 +5741,6 @@
       <c r="J97" t="n">
         <v>1940.04</v>
       </c>
-      <c r="K97" t="n">
-        <v/>
-      </c>
-      <c r="L97" t="n">
-        <v/>
-      </c>
-      <c r="M97" t="n">
-        <v/>
-      </c>
-      <c r="N97" t="n">
-        <v/>
-      </c>
-      <c r="O97" t="n">
-        <v/>
-      </c>
-      <c r="P97" t="n">
-        <v/>
-      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-01; 相对D0=0.95%; 本次触发=2026-05-29(预警买入)</t>
@@ -7220,24 +5792,12 @@
       <c r="J98" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-01; 相对D0=20.36%; 本次触发=2026-05-29(预警买入)</t>
@@ -7289,24 +5849,12 @@
       <c r="J99" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P99" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="5" t="n"/>
+      <c r="M99" s="5" t="n"/>
+      <c r="N99" s="5" t="n"/>
+      <c r="O99" s="5" t="n"/>
+      <c r="P99" s="5" t="n"/>
       <c r="Q99" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-01; 相对D0=6.26%; 本次触发=2026-05-29(预警买入), 2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -7358,24 +5906,12 @@
       <c r="J100" s="5" t="n">
         <v>369.47</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-01; 相对D0=-1.29%; 本次触发=2026-05-29(预警买入)</t>
@@ -7427,24 +5963,12 @@
       <c r="J101" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P101" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="5" t="n"/>
+      <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
       <c r="Q101" s="5" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-01; 相对D0=-1.31%; 本次触发=2026-05-29(正式买入)</t>
@@ -7496,24 +6020,6 @@
       <c r="J102" t="n">
         <v>51.43</v>
       </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-01; 相对D0=-0.29%; 本次触发=2026-05-29(正式买入 | 预警买入)</t>
@@ -7565,24 +6071,6 @@
       <c r="J103" t="n">
         <v>185.67</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7634,24 +6122,6 @@
       <c r="J104" t="n">
         <v>14.7</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -7703,24 +6173,12 @@
       <c r="J105" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7772,24 +6230,6 @@
       <c r="J106" t="n">
         <v>320.41</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -7841,24 +6281,6 @@
       <c r="J107" t="n">
         <v>185.83</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -7910,24 +6332,6 @@
       <c r="J108" t="n">
         <v>136.62</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -7979,24 +6383,6 @@
       <c r="J109" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8048,24 +6434,6 @@
       <c r="J110" t="n">
         <v>27.15</v>
       </c>
-      <c r="K110" t="n">
-        <v/>
-      </c>
-      <c r="L110" t="n">
-        <v/>
-      </c>
-      <c r="M110" t="n">
-        <v/>
-      </c>
-      <c r="N110" t="n">
-        <v/>
-      </c>
-      <c r="O110" t="n">
-        <v/>
-      </c>
-      <c r="P110" t="n">
-        <v/>
-      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8117,24 +6485,6 @@
       <c r="J111" t="n">
         <v>50.55</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8186,27 +6536,15 @@
       <c r="J112" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P112" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K112" s="5" t="n"/>
+      <c r="L112" s="5" t="n"/>
+      <c r="M112" s="5" t="n"/>
+      <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
+      <c r="P112" s="5" t="n"/>
       <c r="Q112" s="5" t="inlineStr">
         <is>
-          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -8255,24 +6593,6 @@
       <c r="J113" t="n">
         <v>905</v>
       </c>
-      <c r="K113" t="n">
-        <v/>
-      </c>
-      <c r="L113" t="n">
-        <v/>
-      </c>
-      <c r="M113" t="n">
-        <v/>
-      </c>
-      <c r="N113" t="n">
-        <v/>
-      </c>
-      <c r="O113" t="n">
-        <v/>
-      </c>
-      <c r="P113" t="n">
-        <v/>
-      </c>
       <c r="Q113" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8324,24 +6644,6 @@
       <c r="J114" t="n">
         <v>11.02</v>
       </c>
-      <c r="K114" t="n">
-        <v/>
-      </c>
-      <c r="L114" t="n">
-        <v/>
-      </c>
-      <c r="M114" t="n">
-        <v/>
-      </c>
-      <c r="N114" t="n">
-        <v/>
-      </c>
-      <c r="O114" t="n">
-        <v/>
-      </c>
-      <c r="P114" t="n">
-        <v/>
-      </c>
       <c r="Q114" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8393,24 +6695,6 @@
       <c r="J115" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="K115" t="n">
-        <v/>
-      </c>
-      <c r="L115" t="n">
-        <v/>
-      </c>
-      <c r="M115" t="n">
-        <v/>
-      </c>
-      <c r="N115" t="n">
-        <v/>
-      </c>
-      <c r="O115" t="n">
-        <v/>
-      </c>
-      <c r="P115" t="n">
-        <v/>
-      </c>
       <c r="Q115" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8462,24 +6746,12 @@
       <c r="J116" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P116" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K116" s="5" t="n"/>
+      <c r="L116" s="5" t="n"/>
+      <c r="M116" s="5" t="n"/>
+      <c r="N116" s="5" t="n"/>
+      <c r="O116" s="5" t="n"/>
+      <c r="P116" s="5" t="n"/>
       <c r="Q116" s="5" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8531,24 +6803,12 @@
       <c r="J117" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P117" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K117" s="5" t="n"/>
+      <c r="L117" s="5" t="n"/>
+      <c r="M117" s="5" t="n"/>
+      <c r="N117" s="5" t="n"/>
+      <c r="O117" s="5" t="n"/>
+      <c r="P117" s="5" t="n"/>
       <c r="Q117" s="5" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8600,24 +6860,6 @@
       <c r="J118" t="n">
         <v>58.92</v>
       </c>
-      <c r="K118" t="n">
-        <v/>
-      </c>
-      <c r="L118" t="n">
-        <v/>
-      </c>
-      <c r="M118" t="n">
-        <v/>
-      </c>
-      <c r="N118" t="n">
-        <v/>
-      </c>
-      <c r="O118" t="n">
-        <v/>
-      </c>
-      <c r="P118" t="n">
-        <v/>
-      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8669,24 +6911,6 @@
       <c r="J119" t="n">
         <v>13.89</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -8738,24 +6962,6 @@
       <c r="J120" t="n">
         <v>15.58</v>
       </c>
-      <c r="K120" t="n">
-        <v/>
-      </c>
-      <c r="L120" t="n">
-        <v/>
-      </c>
-      <c r="M120" t="n">
-        <v/>
-      </c>
-      <c r="N120" t="n">
-        <v/>
-      </c>
-      <c r="O120" t="n">
-        <v/>
-      </c>
-      <c r="P120" t="n">
-        <v/>
-      </c>
       <c r="Q120" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8807,24 +7013,12 @@
       <c r="J121" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P121" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K121" s="5" t="n"/>
+      <c r="L121" s="5" t="n"/>
+      <c r="M121" s="5" t="n"/>
+      <c r="N121" s="5" t="n"/>
+      <c r="O121" s="5" t="n"/>
+      <c r="P121" s="5" t="n"/>
       <c r="Q121" s="5" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8876,24 +7070,6 @@
       <c r="J122" t="n">
         <v>323.39</v>
       </c>
-      <c r="K122" t="n">
-        <v/>
-      </c>
-      <c r="L122" t="n">
-        <v/>
-      </c>
-      <c r="M122" t="n">
-        <v/>
-      </c>
-      <c r="N122" t="n">
-        <v/>
-      </c>
-      <c r="O122" t="n">
-        <v/>
-      </c>
-      <c r="P122" t="n">
-        <v/>
-      </c>
       <c r="Q122" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -8945,24 +7121,6 @@
       <c r="J123" t="n">
         <v>155.71</v>
       </c>
-      <c r="K123" t="n">
-        <v/>
-      </c>
-      <c r="L123" t="n">
-        <v/>
-      </c>
-      <c r="M123" t="n">
-        <v/>
-      </c>
-      <c r="N123" t="n">
-        <v/>
-      </c>
-      <c r="O123" t="n">
-        <v/>
-      </c>
-      <c r="P123" t="n">
-        <v/>
-      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -9010,24 +7168,12 @@
       <c r="J124" s="5" t="n">
         <v>86.68000000000001</v>
       </c>
-      <c r="K124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P124" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="5" t="n"/>
+      <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="5" t="n"/>
       <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-06-01; 相对D0=-2.06%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -9075,24 +7221,12 @@
       <c r="J125" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P125" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K125" s="5" t="n"/>
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="5" t="n"/>
+      <c r="N125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
+      <c r="P125" s="5" t="n"/>
       <c r="Q125" s="5" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-06-01; 相对D0=-6.73%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -9144,24 +7278,12 @@
       <c r="J126" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P126" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K126" s="5" t="n"/>
+      <c r="L126" s="5" t="n"/>
+      <c r="M126" s="5" t="n"/>
+      <c r="N126" s="5" t="n"/>
+      <c r="O126" s="5" t="n"/>
+      <c r="P126" s="5" t="n"/>
       <c r="Q126" s="5" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-01; 相对D0=3.08%</t>
@@ -9209,24 +7331,12 @@
       <c r="J127" s="5" t="n">
         <v>91.03</v>
       </c>
-      <c r="K127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P127" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K127" s="5" t="n"/>
+      <c r="L127" s="5" t="n"/>
+      <c r="M127" s="5" t="n"/>
+      <c r="N127" s="5" t="n"/>
+      <c r="O127" s="5" t="n"/>
+      <c r="P127" s="5" t="n"/>
       <c r="Q127" s="5" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-01; 相对D0=0.18%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -9274,24 +7384,12 @@
       <c r="J128" s="5" t="n">
         <v>38.79</v>
       </c>
-      <c r="K128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="5" t="n"/>
+      <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="5" t="n"/>
       <c r="Q128" s="5" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-06-01; 相对D0=-6.19%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -9339,24 +7437,12 @@
       <c r="J129" s="5" t="n">
         <v>91.03</v>
       </c>
-      <c r="K129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P129" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K129" s="5" t="n"/>
+      <c r="L129" s="5" t="n"/>
+      <c r="M129" s="5" t="n"/>
+      <c r="N129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
+      <c r="P129" s="5" t="n"/>
       <c r="Q129" s="5" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-01; 相对D0=-0.07%</t>
@@ -9404,24 +7490,12 @@
       <c r="J130" s="5" t="n">
         <v>1050.77</v>
       </c>
-      <c r="K130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P130" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K130" s="5" t="n"/>
+      <c r="L130" s="5" t="n"/>
+      <c r="M130" s="5" t="n"/>
+      <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
+      <c r="P130" s="5" t="n"/>
       <c r="Q130" s="5" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-01; 相对D0=-1.75%</t>
@@ -9469,24 +7543,12 @@
       <c r="J131" s="5" t="n">
         <v>86.68000000000001</v>
       </c>
-      <c r="K131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P131" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K131" s="5" t="n"/>
+      <c r="L131" s="5" t="n"/>
+      <c r="M131" s="5" t="n"/>
+      <c r="N131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="5" t="n"/>
       <c r="Q131" s="5" t="inlineStr">
         <is>
           <t>D0=87.18; 最新=2026-06-01; 相对D0=-0.57%</t>
@@ -9534,24 +7596,12 @@
       <c r="J132" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P132" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K132" s="5" t="n"/>
+      <c r="L132" s="5" t="n"/>
+      <c r="M132" s="5" t="n"/>
+      <c r="N132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
+      <c r="P132" s="5" t="n"/>
       <c r="Q132" s="5" t="inlineStr">
         <is>
           <t>D0=150.11; 最新=2026-06-01; 相对D0=-1.61%</t>
@@ -9599,24 +7649,12 @@
       <c r="J133" s="5" t="n">
         <v>86.68000000000001</v>
       </c>
-      <c r="K133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P133" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K133" s="5" t="n"/>
+      <c r="L133" s="5" t="n"/>
+      <c r="M133" s="5" t="n"/>
+      <c r="N133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="5" t="n"/>
       <c r="Q133" s="5" t="inlineStr">
         <is>
           <t>D0=89.49; 最新=2026-06-01; 相对D0=-3.14%</t>
@@ -9664,24 +7702,12 @@
       <c r="J134" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P134" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K134" s="5" t="n"/>
+      <c r="L134" s="5" t="n"/>
+      <c r="M134" s="5" t="n"/>
+      <c r="N134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
+      <c r="P134" s="5" t="n"/>
       <c r="Q134" s="5" t="inlineStr">
         <is>
           <t>D0=163.35; 最新=2026-06-01; 相对D0=-9.59%</t>
@@ -9733,24 +7759,6 @@
       <c r="J135" t="n">
         <v>115.58</v>
       </c>
-      <c r="K135" t="n">
-        <v/>
-      </c>
-      <c r="L135" t="n">
-        <v/>
-      </c>
-      <c r="M135" t="n">
-        <v/>
-      </c>
-      <c r="N135" t="n">
-        <v/>
-      </c>
-      <c r="O135" t="n">
-        <v/>
-      </c>
-      <c r="P135" t="n">
-        <v/>
-      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -9798,24 +7806,12 @@
       <c r="J136" s="5" t="n">
         <v>99.18600000000001</v>
       </c>
-      <c r="K136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="5" t="n"/>
+      <c r="N136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
+      <c r="P136" s="5" t="n"/>
       <c r="Q136" s="5" t="inlineStr">
         <is>
           <t>D0=99.19; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -9863,24 +7859,12 @@
       <c r="J137" s="5" t="n">
         <v>38.79</v>
       </c>
-      <c r="K137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O137" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P137" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K137" s="5" t="n"/>
+      <c r="L137" s="5" t="n"/>
+      <c r="M137" s="5" t="n"/>
+      <c r="N137" s="5" t="n"/>
+      <c r="O137" s="5" t="n"/>
+      <c r="P137" s="5" t="n"/>
       <c r="Q137" s="5" t="inlineStr">
         <is>
           <t>D0=38.79; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -9928,24 +7912,12 @@
       <c r="J138" s="5" t="n">
         <v>16.05</v>
       </c>
-      <c r="K138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P138" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K138" s="5" t="n"/>
+      <c r="L138" s="5" t="n"/>
+      <c r="M138" s="5" t="n"/>
+      <c r="N138" s="5" t="n"/>
+      <c r="O138" s="5" t="n"/>
+      <c r="P138" s="5" t="n"/>
       <c r="Q138" s="5" t="inlineStr">
         <is>
           <t>D0=16.05; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -10182,24 +8154,12 @@
       <c r="J150" s="5" t="n">
         <v>39.35</v>
       </c>
-      <c r="K150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P150" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K150" s="5" t="n"/>
+      <c r="L150" s="5" t="n"/>
+      <c r="M150" s="5" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="5" t="n"/>
       <c r="Q150" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-01; 相对D0=-5.11%; 本次触发=2026-05-22(正式卖出)</t>
@@ -10251,24 +8211,12 @@
       <c r="J151" s="5" t="n">
         <v>185.83</v>
       </c>
-      <c r="K151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P151" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K151" s="5" t="n"/>
+      <c r="L151" s="5" t="n"/>
+      <c r="M151" s="5" t="n"/>
+      <c r="N151" s="5" t="n"/>
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="5" t="n"/>
       <c r="Q151" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-01; 相对D0=0.61%; 本次触发=2026-05-26(正式卖出)</t>
@@ -10320,24 +8268,12 @@
       <c r="J152" s="5" t="n">
         <v>136.62</v>
       </c>
-      <c r="K152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P152" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K152" s="5" t="n"/>
+      <c r="L152" s="5" t="n"/>
+      <c r="M152" s="5" t="n"/>
+      <c r="N152" s="5" t="n"/>
+      <c r="O152" s="5" t="n"/>
+      <c r="P152" s="5" t="n"/>
       <c r="Q152" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-01; 相对D0=0.31%; 本次触发=2026-05-26(正式卖出)</t>
@@ -10389,24 +8325,6 @@
       <c r="J153" t="n">
         <v>403.88</v>
       </c>
-      <c r="K153" t="n">
-        <v/>
-      </c>
-      <c r="L153" t="n">
-        <v/>
-      </c>
-      <c r="M153" t="n">
-        <v/>
-      </c>
-      <c r="N153" t="n">
-        <v/>
-      </c>
-      <c r="O153" t="n">
-        <v/>
-      </c>
-      <c r="P153" t="n">
-        <v/>
-      </c>
       <c r="Q153" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-01; 相对D0=31.41%; 本次触发=2026-05-26(正式卖出)</t>
@@ -10458,24 +8376,12 @@
       <c r="J154" s="5" t="n">
         <v>58.92</v>
       </c>
-      <c r="K154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P154" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K154" s="5" t="n"/>
+      <c r="L154" s="5" t="n"/>
+      <c r="M154" s="5" t="n"/>
+      <c r="N154" s="5" t="n"/>
+      <c r="O154" s="5" t="n"/>
+      <c r="P154" s="5" t="n"/>
       <c r="Q154" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-01; 相对D0=2.54%; 本次触发=2026-05-26(正式卖出)</t>
@@ -10527,24 +8433,12 @@
       <c r="J155" s="5" t="n">
         <v>13.89</v>
       </c>
-      <c r="K155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P155" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K155" s="5" t="n"/>
+      <c r="L155" s="5" t="n"/>
+      <c r="M155" s="5" t="n"/>
+      <c r="N155" s="5" t="n"/>
+      <c r="O155" s="5" t="n"/>
+      <c r="P155" s="5" t="n"/>
       <c r="Q155" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-01; 相对D0=4.04%; 本次触发=2026-05-26(正式卖出)</t>
@@ -10596,24 +8490,12 @@
       <c r="J156" s="5" t="n">
         <v>57.3</v>
       </c>
-      <c r="K156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P156" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K156" s="5" t="n"/>
+      <c r="L156" s="5" t="n"/>
+      <c r="M156" s="5" t="n"/>
+      <c r="N156" s="5" t="n"/>
+      <c r="O156" s="5" t="n"/>
+      <c r="P156" s="5" t="n"/>
       <c r="Q156" s="5" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-01; 相对D0=-0.95%; 本次触发=2026-05-26(正式卖出)</t>
@@ -10665,24 +8547,12 @@
       <c r="J157" s="5" t="n">
         <v>54.75</v>
       </c>
-      <c r="K157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P157" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K157" s="5" t="n"/>
+      <c r="L157" s="5" t="n"/>
+      <c r="M157" s="5" t="n"/>
+      <c r="N157" s="5" t="n"/>
+      <c r="O157" s="5" t="n"/>
+      <c r="P157" s="5" t="n"/>
       <c r="Q157" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-01; 相对D0=-3.10%; 本次触发=2026-05-27(正式卖出 | 预警卖出)</t>
@@ -10734,24 +8604,6 @@
       <c r="J158" t="n">
         <v>155.71</v>
       </c>
-      <c r="K158" t="n">
-        <v/>
-      </c>
-      <c r="L158" t="n">
-        <v/>
-      </c>
-      <c r="M158" t="n">
-        <v/>
-      </c>
-      <c r="N158" t="n">
-        <v/>
-      </c>
-      <c r="O158" t="n">
-        <v/>
-      </c>
-      <c r="P158" t="n">
-        <v/>
-      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-01; 相对D0=23.18%; 本次触发=2026-05-27(正式卖出 | 预警卖出)</t>
@@ -10803,24 +8655,12 @@
       <c r="J159" s="5" t="n">
         <v>109.55</v>
       </c>
-      <c r="K159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P159" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K159" s="5" t="n"/>
+      <c r="L159" s="5" t="n"/>
+      <c r="M159" s="5" t="n"/>
+      <c r="N159" s="5" t="n"/>
+      <c r="O159" s="5" t="n"/>
+      <c r="P159" s="5" t="n"/>
       <c r="Q159" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-01; 相对D0=-5.32%; 本次触发=2026-05-28(正式卖出)</t>
@@ -10872,24 +8712,6 @@
       <c r="J160" t="n">
         <v>265.7</v>
       </c>
-      <c r="K160" t="n">
-        <v/>
-      </c>
-      <c r="L160" t="n">
-        <v/>
-      </c>
-      <c r="M160" t="n">
-        <v/>
-      </c>
-      <c r="N160" t="n">
-        <v/>
-      </c>
-      <c r="O160" t="n">
-        <v/>
-      </c>
-      <c r="P160" t="n">
-        <v/>
-      </c>
       <c r="Q160" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-01; 相对D0=-7.20%; 本次触发=2026-05-28(正式卖出)</t>
@@ -10941,24 +8763,12 @@
       <c r="J161" s="5" t="n">
         <v>176.7</v>
       </c>
-      <c r="K161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P161" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K161" s="5" t="n"/>
+      <c r="L161" s="5" t="n"/>
+      <c r="M161" s="5" t="n"/>
+      <c r="N161" s="5" t="n"/>
+      <c r="O161" s="5" t="n"/>
+      <c r="P161" s="5" t="n"/>
       <c r="Q161" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-01; 相对D0=-3.43%; 本次触发=2026-05-28(正式卖出)</t>
@@ -11010,24 +8820,6 @@
       <c r="J162" t="n">
         <v>492.29</v>
       </c>
-      <c r="K162" t="n">
-        <v/>
-      </c>
-      <c r="L162" t="n">
-        <v/>
-      </c>
-      <c r="M162" t="n">
-        <v/>
-      </c>
-      <c r="N162" t="n">
-        <v/>
-      </c>
-      <c r="O162" t="n">
-        <v/>
-      </c>
-      <c r="P162" t="n">
-        <v/>
-      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-01; 相对D0=2.42%; 本次触发=2026-05-28(正式卖出 | 预警卖出)</t>
@@ -11079,24 +8871,12 @@
       <c r="J163" s="5" t="n">
         <v>93.62</v>
       </c>
-      <c r="K163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P163" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K163" s="5" t="n"/>
+      <c r="L163" s="5" t="n"/>
+      <c r="M163" s="5" t="n"/>
+      <c r="N163" s="5" t="n"/>
+      <c r="O163" s="5" t="n"/>
+      <c r="P163" s="5" t="n"/>
       <c r="Q163" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-01; 相对D0=1.40%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -11148,24 +8928,12 @@
       <c r="J164" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P164" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K164" s="5" t="n"/>
+      <c r="L164" s="5" t="n"/>
+      <c r="M164" s="5" t="n"/>
+      <c r="N164" s="5" t="n"/>
+      <c r="O164" s="5" t="n"/>
+      <c r="P164" s="5" t="n"/>
       <c r="Q164" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-01; 相对D0=4.59%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -11217,24 +8985,12 @@
       <c r="J165" s="5" t="n">
         <v>273.51</v>
       </c>
-      <c r="K165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P165" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K165" s="5" t="n"/>
+      <c r="L165" s="5" t="n"/>
+      <c r="M165" s="5" t="n"/>
+      <c r="N165" s="5" t="n"/>
+      <c r="O165" s="5" t="n"/>
+      <c r="P165" s="5" t="n"/>
       <c r="Q165" s="5" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-01; 相对D0=-4.03%; 本次触发=2026-05-29(正式卖出)</t>
@@ -11286,24 +9042,12 @@
       <c r="J166" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P166" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K166" s="5" t="n"/>
+      <c r="L166" s="5" t="n"/>
+      <c r="M166" s="5" t="n"/>
+      <c r="N166" s="5" t="n"/>
+      <c r="O166" s="5" t="n"/>
+      <c r="P166" s="5" t="n"/>
       <c r="Q166" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%; 本次触发=2026-05-29(预警卖出), 2026-06-01(正式卖出); 历史重复1次; 重复日期=2026-06-01</t>
@@ -11355,24 +9099,12 @@
       <c r="J167" s="5" t="n">
         <v>362.9</v>
       </c>
-      <c r="K167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P167" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K167" s="5" t="n"/>
+      <c r="L167" s="5" t="n"/>
+      <c r="M167" s="5" t="n"/>
+      <c r="N167" s="5" t="n"/>
+      <c r="O167" s="5" t="n"/>
+      <c r="P167" s="5" t="n"/>
       <c r="Q167" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-01; 相对D0=0.40%; 本次触发=2026-05-29(正式卖出)</t>
@@ -11424,24 +9156,12 @@
       <c r="J168" s="5" t="n">
         <v>27.15</v>
       </c>
-      <c r="K168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P168" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K168" s="5" t="n"/>
+      <c r="L168" s="5" t="n"/>
+      <c r="M168" s="5" t="n"/>
+      <c r="N168" s="5" t="n"/>
+      <c r="O168" s="5" t="n"/>
+      <c r="P168" s="5" t="n"/>
       <c r="Q168" s="5" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-01; 相对D0=43.80%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -11493,24 +9213,6 @@
       <c r="J169" t="n">
         <v>109.33</v>
       </c>
-      <c r="K169" t="n">
-        <v/>
-      </c>
-      <c r="L169" t="n">
-        <v/>
-      </c>
-      <c r="M169" t="n">
-        <v/>
-      </c>
-      <c r="N169" t="n">
-        <v/>
-      </c>
-      <c r="O169" t="n">
-        <v/>
-      </c>
-      <c r="P169" t="n">
-        <v/>
-      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-01; 相对D0=-4.67%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -11562,24 +9264,12 @@
       <c r="J170" s="5" t="n">
         <v>129.47</v>
       </c>
-      <c r="K170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P170" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K170" s="5" t="n"/>
+      <c r="L170" s="5" t="n"/>
+      <c r="M170" s="5" t="n"/>
+      <c r="N170" s="5" t="n"/>
+      <c r="O170" s="5" t="n"/>
+      <c r="P170" s="5" t="n"/>
       <c r="Q170" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-01; 相对D0=-3.44%; 本次触发=2026-05-29(正式卖出 | 预警卖出)</t>
@@ -11631,24 +9321,12 @@
       <c r="J171" s="5" t="n">
         <v>252.53</v>
       </c>
-      <c r="K171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P171" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K171" s="5" t="n"/>
+      <c r="L171" s="5" t="n"/>
+      <c r="M171" s="5" t="n"/>
+      <c r="N171" s="5" t="n"/>
+      <c r="O171" s="5" t="n"/>
+      <c r="P171" s="5" t="n"/>
       <c r="Q171" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-01; 相对D0=-1.06%; 本次触发=2026-05-29(正式卖出)</t>
@@ -11700,24 +9378,6 @@
       <c r="J172" t="n">
         <v>105.65</v>
       </c>
-      <c r="K172" t="n">
-        <v/>
-      </c>
-      <c r="L172" t="n">
-        <v/>
-      </c>
-      <c r="M172" t="n">
-        <v/>
-      </c>
-      <c r="N172" t="n">
-        <v/>
-      </c>
-      <c r="O172" t="n">
-        <v/>
-      </c>
-      <c r="P172" t="n">
-        <v/>
-      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -11769,24 +9429,12 @@
       <c r="J173" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P173" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K173" s="5" t="n"/>
+      <c r="L173" s="5" t="n"/>
+      <c r="M173" s="5" t="n"/>
+      <c r="N173" s="5" t="n"/>
+      <c r="O173" s="5" t="n"/>
+      <c r="P173" s="5" t="n"/>
       <c r="Q173" s="5" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -11838,24 +9486,6 @@
       <c r="J174" t="n">
         <v>64.61</v>
       </c>
-      <c r="K174" t="n">
-        <v/>
-      </c>
-      <c r="L174" t="n">
-        <v/>
-      </c>
-      <c r="M174" t="n">
-        <v/>
-      </c>
-      <c r="N174" t="n">
-        <v/>
-      </c>
-      <c r="O174" t="n">
-        <v/>
-      </c>
-      <c r="P174" t="n">
-        <v/>
-      </c>
       <c r="Q174" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -11907,24 +9537,12 @@
       <c r="J175" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P175" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K175" s="5" t="n"/>
+      <c r="L175" s="5" t="n"/>
+      <c r="M175" s="5" t="n"/>
+      <c r="N175" s="5" t="n"/>
+      <c r="O175" s="5" t="n"/>
+      <c r="P175" s="5" t="n"/>
       <c r="Q175" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -11976,24 +9594,6 @@
       <c r="J176" t="n">
         <v>600.47</v>
       </c>
-      <c r="K176" t="n">
-        <v/>
-      </c>
-      <c r="L176" t="n">
-        <v/>
-      </c>
-      <c r="M176" t="n">
-        <v/>
-      </c>
-      <c r="N176" t="n">
-        <v/>
-      </c>
-      <c r="O176" t="n">
-        <v/>
-      </c>
-      <c r="P176" t="n">
-        <v/>
-      </c>
       <c r="Q176" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -12045,24 +9645,12 @@
       <c r="J177" s="5" t="n">
         <v>24.86</v>
       </c>
-      <c r="K177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P177" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K177" s="5" t="n"/>
+      <c r="L177" s="5" t="n"/>
+      <c r="M177" s="5" t="n"/>
+      <c r="N177" s="5" t="n"/>
+      <c r="O177" s="5" t="n"/>
+      <c r="P177" s="5" t="n"/>
       <c r="Q177" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -12114,24 +9702,6 @@
       <c r="J178" t="n">
         <v>415.88</v>
       </c>
-      <c r="K178" t="n">
-        <v/>
-      </c>
-      <c r="L178" t="n">
-        <v/>
-      </c>
-      <c r="M178" t="n">
-        <v/>
-      </c>
-      <c r="N178" t="n">
-        <v/>
-      </c>
-      <c r="O178" t="n">
-        <v/>
-      </c>
-      <c r="P178" t="n">
-        <v/>
-      </c>
       <c r="Q178" t="inlineStr">
         <is>
           <t>D0=415.88; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -12152,7 +9722,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -12179,24 +9748,6 @@
       <c r="J179" t="n">
         <v>91.03</v>
       </c>
-      <c r="K179" t="n">
-        <v/>
-      </c>
-      <c r="L179" t="n">
-        <v/>
-      </c>
-      <c r="M179" t="n">
-        <v/>
-      </c>
-      <c r="N179" t="n">
-        <v/>
-      </c>
-      <c r="O179" t="n">
-        <v/>
-      </c>
-      <c r="P179" t="n">
-        <v/>
-      </c>
       <c r="Q179" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-01; 相对D0=0.43%</t>
@@ -12217,7 +9768,6 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -12243,24 +9793,6 @@
       </c>
       <c r="J180" t="n">
         <v>38.79</v>
-      </c>
-      <c r="K180" t="n">
-        <v/>
-      </c>
-      <c r="L180" t="n">
-        <v/>
-      </c>
-      <c r="M180" t="n">
-        <v/>
-      </c>
-      <c r="N180" t="n">
-        <v/>
-      </c>
-      <c r="O180" t="n">
-        <v/>
-      </c>
-      <c r="P180" t="n">
-        <v/>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -12358,7 +9890,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12370,7 +9901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -12645,7 +10176,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -12693,7 +10224,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
@@ -12851,7 +10382,6 @@
       <c r="F10" t="n">
         <v>190.96</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>203.7</v>
       </c>
@@ -12870,7 +10400,6 @@
       <c r="M10" s="11" t="n">
         <v>0.299487</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -13026,7 +10555,6 @@
       <c r="M13" s="19" t="n">
         <v>-0.04189</v>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -13304,9 +10832,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -13352,9 +10878,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="21" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -13445,10 +10969,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13460,7 +10980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -14042,7 +11562,6 @@
       <c r="K13" s="11" t="n">
         <v>0.16807</v>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14088,7 +11607,6 @@
       <c r="K14" s="11" t="n">
         <v>0.069425</v>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14117,7 +11635,6 @@
       <c r="F15" t="n">
         <v>290.01</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>285</v>
       </c>
@@ -14130,7 +11647,6 @@
       <c r="K15" s="19" t="n">
         <v>-0.056895</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -14205,7 +11721,6 @@
       <c r="F17" t="n">
         <v>67.38</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>66.94</v>
       </c>
@@ -14218,7 +11733,6 @@
       <c r="K17" s="19" t="n">
         <v>-0.04111</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -14373,7 +11887,6 @@
       <c r="F21" t="n">
         <v>226.34</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>231.09</v>
       </c>
@@ -14386,7 +11899,6 @@
       <c r="K21" s="11" t="n">
         <v>0.16864</v>
       </c>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -14722,9 +12234,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="21" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -14764,9 +12274,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="21" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -14806,9 +12314,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -14848,9 +12354,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="21" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -14948,9 +12452,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14962,7 +12463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -15209,7 +12710,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
@@ -15462,7 +12963,6 @@
       <c r="I13" s="11" t="n">
         <v>0.139596</v>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -15607,14 +13107,12 @@
       <c r="F17" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1940.04</v>
       </c>
       <c r="I17" s="11" t="n">
         <v>0.009538</v>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -15772,9 +13270,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="21" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -15808,9 +13304,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="21" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -15844,9 +13338,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="21" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -15880,9 +13372,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="21" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -15920,9 +13410,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -15956,9 +13444,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="21" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -15992,9 +13478,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -16028,9 +13512,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="21" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -16064,9 +13546,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="21" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -16184,7 +13664,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16196,7 +13675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -16313,7 +13792,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F4" s="12" t="n">
@@ -16473,8 +13952,6 @@
       <c r="F9" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -16593,8 +14070,6 @@
       <c r="F13" t="n">
         <v>14.7</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -16691,8 +14166,6 @@
       <c r="F16" t="n">
         <v>15.58</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -16790,7 +14263,6 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -17198,9 +14670,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -17228,9 +14698,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="21" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17262,9 +14730,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -17292,9 +14758,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="21" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17322,9 +14786,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="21" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -17352,9 +14814,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="21" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -17382,9 +14842,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="21" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -17496,7 +14954,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17804,7 +15261,6 @@
       <c r="V3" t="n">
         <v>85.45999908447266</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.78; 4H分金=49.43</t>
@@ -17886,8 +15342,6 @@
       <c r="T4" t="b">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
         <v>91</v>
       </c>
@@ -17972,8 +15426,6 @@
       <c r="T5" t="b">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
         <v>90</v>
       </c>
@@ -18012,7 +15464,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -18238,8 +15690,6 @@
       <c r="T8" t="b">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
         <v>90</v>
       </c>
@@ -18504,9 +15954,6 @@
       <c r="T11" t="b">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.16; 4H分金=48.27</t>
@@ -18588,8 +16035,6 @@
       <c r="T12" t="b">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
         <v>86</v>
       </c>
@@ -18854,8 +16299,6 @@
       <c r="T15" t="b">
         <v>0</v>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
         <v>90</v>
       </c>
@@ -18940,9 +16383,6 @@
       <c r="T16" t="b">
         <v>1</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.07; 4H分金=49.33</t>
@@ -19030,7 +16470,6 @@
       <c r="V17" t="n">
         <v>43.59000015258789</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=43.59; Gann0=38.83; 段涨幅=12.26%</t>
@@ -19292,8 +16731,6 @@
       <c r="T20" t="b">
         <v>0</v>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
         <v>98</v>
       </c>
@@ -19468,8 +16905,6 @@
       <c r="T22" t="b">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="n">
         <v>89</v>
       </c>
@@ -19598,7 +17033,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -19688,7 +17123,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -20094,8 +17529,6 @@
       <c r="T29" t="b">
         <v>0</v>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="n">
         <v>88</v>
       </c>
@@ -20270,8 +17703,6 @@
       <c r="T31" t="b">
         <v>0</v>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="n">
         <v>91</v>
       </c>
@@ -20362,7 +17793,6 @@
       <c r="V32" t="n">
         <v>15.39999961853027</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.98; 4H分金=49.65</t>
@@ -20450,7 +17880,6 @@
       <c r="V33" t="n">
         <v>105.5599975585938</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.29; 4H分金=48.73</t>
@@ -20532,8 +17961,6 @@
       <c r="T34" t="b">
         <v>0</v>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
         <v>86</v>
       </c>
@@ -20888,8 +18315,6 @@
       <c r="T38" t="b">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
         <v>98</v>
       </c>
@@ -21108,7 +18533,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -21244,8 +18669,6 @@
       <c r="T42" t="b">
         <v>0</v>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="n">
         <v>88</v>
       </c>
@@ -21336,7 +18759,6 @@
       <c r="V43" t="n">
         <v>194.9600067138672</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.57; 4H分金=48.78</t>
@@ -21604,7 +19026,6 @@
       <c r="V46" t="n">
         <v>269.7900085449219</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.14; 4H分金=49.53</t>
@@ -21692,7 +19113,6 @@
       <c r="V47" t="n">
         <v>330.2200012207031</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.16; 4H分金=41.08</t>
@@ -22044,8 +19464,6 @@
       <c r="T51" t="b">
         <v>0</v>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="n">
         <v>89</v>
       </c>
@@ -22220,8 +19638,6 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
         <v>90</v>
       </c>
@@ -22306,8 +19722,6 @@
       <c r="T54" t="b">
         <v>0</v>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="n">
         <v>94</v>
       </c>
@@ -22398,7 +19812,6 @@
       <c r="V55" t="n">
         <v>198.8699951171875</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-19; 1出价格=198.87; Gann0=179.53; 段涨幅=10.77%</t>
@@ -22576,7 +19989,6 @@
       <c r="V57" t="n">
         <v>145.6999969482422</v>
       </c>
-      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=145.70; Gann0=128.83; 段涨幅=13.09%</t>
@@ -23114,7 +20526,6 @@
       <c r="V63" t="n">
         <v>977.27001953125</v>
       </c>
-      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.01; 4H分金=41.40</t>
@@ -23196,9 +20607,6 @@
       <c r="T64" t="b">
         <v>1</v>
       </c>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=40.99; 4H分金=34.86</t>
@@ -23376,7 +20784,6 @@
       <c r="V66" t="n">
         <v>349.2099914550781</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-19; 1出价格=349.21; Gann0=244.88; 段涨幅=42.60%</t>
@@ -23502,7 +20909,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -23644,7 +21051,6 @@
       <c r="V69" t="n">
         <v>226.8099975585938</v>
       </c>
-      <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.20; 4H分金=48.61</t>
@@ -23822,7 +21228,6 @@
       <c r="V71" t="n">
         <v>110.8300018310547</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.16; 4H分金=48.24</t>
@@ -23858,7 +21263,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -24180,7 +21585,6 @@
       <c r="V75" t="n">
         <v>61.2400016784668</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=61.24; Gann0=52.99; 段涨幅=15.57%</t>
@@ -24358,7 +21762,6 @@
       <c r="V77" t="n">
         <v>15.39999961853027</v>
       </c>
-      <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-22; 1出价格=15.40; Gann0=11.82; 段涨幅=30.29%</t>
@@ -24574,7 +21977,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -24754,7 +22157,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -25166,7 +22569,6 @@
       <c r="V86" t="n">
         <v>88.55000305175781</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.93; 4H分金=48.13</t>
@@ -25248,8 +22650,6 @@
       <c r="T87" t="b">
         <v>0</v>
       </c>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
       <c r="W87" t="n">
         <v>100</v>
       </c>
@@ -25430,7 +22830,6 @@
       <c r="V89" t="n">
         <v>61.70000076293945</v>
       </c>
-      <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-20; 1出价格=61.70; Gann0=55.13; 段涨幅=11.92%</t>
@@ -25878,7 +23277,6 @@
       <c r="V94" t="n">
         <v>143.1600036621094</v>
       </c>
-      <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.24; 4H分金=47.86</t>
@@ -25966,7 +23364,6 @@
       <c r="V95" t="n">
         <v>322.8299865722656</v>
       </c>
-      <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.51; 4H分金=46.81</t>
@@ -26054,7 +23451,6 @@
       <c r="V96" t="n">
         <v>310.4500122070312</v>
       </c>
-      <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.07; 4H分金=49.25</t>
@@ -26142,7 +23538,6 @@
       <c r="V97" t="n">
         <v>84.98999786376953</v>
       </c>
-      <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=65.41; 4H分金=46.13</t>
@@ -26410,7 +23805,6 @@
       <c r="V100" t="n">
         <v>183.9199981689453</v>
       </c>
-      <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.34; 4H分金=45.78</t>
@@ -26498,7 +23892,6 @@
       <c r="V101" t="n">
         <v>677.5</v>
       </c>
-      <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=69.20; 4H分金=49.77</t>
@@ -26586,7 +23979,6 @@
       <c r="V102" t="n">
         <v>68.97000122070312</v>
       </c>
-      <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.29; 4H分金=51.57</t>
@@ -26674,7 +24066,6 @@
       <c r="V103" t="n">
         <v>50.5</v>
       </c>
-      <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.87; 4H分金=41.41</t>
@@ -26762,7 +24153,6 @@
       <c r="V104" t="n">
         <v>134.9100036621094</v>
       </c>
-      <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=65.12; 4H分金=42.03</t>
@@ -26850,7 +24240,6 @@
       <c r="V105" t="n">
         <v>199.9299926757812</v>
       </c>
-      <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.09; 4H分金=49.59</t>
@@ -26976,7 +24365,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -27298,7 +24687,6 @@
       <c r="V110" t="n">
         <v>94.91999816894531</v>
       </c>
-      <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.51; 4H分金=49.40</t>
@@ -27560,9 +24948,6 @@
       <c r="T113" t="b">
         <v>1</v>
       </c>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.82; 4H分金=47.70</t>
@@ -27650,7 +25035,6 @@
       <c r="V114" t="n">
         <v>521.22998046875</v>
       </c>
-      <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.81; 4H分金=33.44</t>
@@ -27828,7 +25212,6 @@
       <c r="V116" t="n">
         <v>96.38999938964844</v>
       </c>
-      <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.32; 4H分金=47.38</t>
@@ -28096,7 +25479,6 @@
       <c r="V119" t="n">
         <v>197</v>
       </c>
-      <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.96; 4H分金=52.74</t>
@@ -28184,7 +25566,6 @@
       <c r="V120" t="n">
         <v>261.4100036621094</v>
       </c>
-      <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=64.28; 4H分金=46.06</t>
@@ -28272,7 +25653,6 @@
       <c r="V121" t="n">
         <v>139.0200042724609</v>
       </c>
-      <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=39.09; 4H分金=22.70</t>
@@ -28360,7 +25740,6 @@
       <c r="V122" t="n">
         <v>58.81999969482422</v>
       </c>
-      <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=58.82; Gann0=52.73; 段涨幅=11.55%</t>
@@ -28448,7 +25827,6 @@
       <c r="V123" t="n">
         <v>58.81999969482422</v>
       </c>
-      <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.71; 4H分金=39.07</t>
@@ -28574,7 +25952,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -28800,8 +26178,6 @@
       <c r="T127" t="b">
         <v>0</v>
       </c>
-      <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
       <c r="W127" t="n">
         <v>81</v>
       </c>
@@ -28892,7 +26268,6 @@
       <c r="V128" t="n">
         <v>191.25</v>
       </c>
-      <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=191.25; Gann0=127.79; 段涨幅=49.66%</t>
@@ -28980,7 +26355,6 @@
       <c r="V129" t="n">
         <v>191.25</v>
       </c>
-      <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=31.56; 4H分金=18.97</t>
@@ -29068,7 +26442,6 @@
       <c r="V130" t="n">
         <v>143.1600036621094</v>
       </c>
-      <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=143.16; Gann0=101.88; 段涨幅=40.52%</t>
@@ -29336,7 +26709,6 @@
       <c r="V133" t="n">
         <v>310.4500122070312</v>
       </c>
-      <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=310.45; Gann0=256.10; 段涨幅=21.22%</t>
@@ -29514,7 +26886,6 @@
       <c r="V135" t="n">
         <v>393.5199890136719</v>
       </c>
-      <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.60; 4H分金=49.67</t>
@@ -29596,8 +26967,6 @@
       <c r="T136" t="b">
         <v>0</v>
       </c>
-      <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
       <c r="W136" t="n">
         <v>96</v>
       </c>
@@ -29772,8 +27141,6 @@
       <c r="T138" t="b">
         <v>0</v>
       </c>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
       <c r="W138" t="n">
         <v>85</v>
       </c>
@@ -29954,7 +27321,6 @@
       <c r="V140" t="n">
         <v>125.9499969482422</v>
       </c>
-      <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.41; 4H分金=33.44</t>
@@ -30132,7 +27498,6 @@
       <c r="V142" t="n">
         <v>199.9299926757812</v>
       </c>
-      <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=199.93; Gann0=169.80; 段涨幅=17.74%</t>
@@ -31660,7 +29025,6 @@
       <c r="V159" t="n">
         <v>539.47998046875</v>
       </c>
-      <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=539.48; Gann0=473.77; 段涨幅=13.87%</t>
@@ -31748,7 +29112,6 @@
       <c r="V160" t="n">
         <v>539.47998046875</v>
       </c>
-      <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=38.34; 4H分金=25.68</t>
@@ -31836,7 +29199,6 @@
       <c r="V161" t="n">
         <v>302.8599853515625</v>
       </c>
-      <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.03; 4H分金=49.91</t>
@@ -31924,7 +29286,6 @@
       <c r="V162" t="n">
         <v>45.63999938964844</v>
       </c>
-      <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=42.99; 4H分金=32.45</t>
@@ -32050,7 +29411,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -32282,7 +29643,6 @@
       <c r="V166" t="n">
         <v>112</v>
       </c>
-      <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=112.00; Gann0=76.76; 段涨幅=45.91%</t>
@@ -32370,7 +29730,6 @@
       <c r="V167" t="n">
         <v>112</v>
       </c>
-      <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.51; 4H分金=34.98</t>
@@ -32458,7 +29817,6 @@
       <c r="V168" t="n">
         <v>14.73999977111816</v>
       </c>
-      <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=63.89; 4H分金=51.21</t>
@@ -32546,7 +29904,6 @@
       <c r="V169" t="n">
         <v>76.30000305175781</v>
       </c>
-      <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=76.30; Gann0=62.45; 段涨幅=22.18%</t>
@@ -32634,7 +29991,6 @@
       <c r="V170" t="n">
         <v>76.30000305175781</v>
       </c>
-      <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.17; 4H分金=45.51</t>
@@ -32722,7 +30078,6 @@
       <c r="V171" t="n">
         <v>133.8600006103516</v>
       </c>
-      <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.46; 4H分金=46.97</t>
@@ -32810,7 +30165,6 @@
       <c r="V172" t="n">
         <v>322.8299865722656</v>
       </c>
-      <c r="W172" t="inlineStr"/>
       <c r="X172" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-22; 1出价格=322.83; Gann0=241.75; 段涨幅=33.54%</t>
@@ -32988,7 +30342,6 @@
       <c r="V174" t="n">
         <v>178.9100036621094</v>
       </c>
-      <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.41; 4H分金=56.01</t>
@@ -33166,7 +30519,6 @@
       <c r="V176" t="n">
         <v>393.5199890136719</v>
       </c>
-      <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=393.52; Gann0=336.70; 段涨幅=16.88%</t>
@@ -33884,7 +31236,6 @@
       <c r="V184" t="n">
         <v>9.319999694824219</v>
       </c>
-      <c r="W184" t="inlineStr"/>
       <c r="X184" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.35; 4H分金=48.97</t>
@@ -33972,7 +31323,6 @@
       <c r="V185" t="n">
         <v>22.48999977111816</v>
       </c>
-      <c r="W185" t="inlineStr"/>
       <c r="X185" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-22; 1出价格=22.49; Gann0=17.23; 段涨幅=30.51%</t>
@@ -34060,7 +31410,6 @@
       <c r="V186" t="n">
         <v>22.48999977111816</v>
       </c>
-      <c r="W186" t="inlineStr"/>
       <c r="X186" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.73; 4H分金=28.42</t>
@@ -34148,7 +31497,6 @@
       <c r="V187" t="n">
         <v>391.8699951171875</v>
       </c>
-      <c r="W187" t="inlineStr"/>
       <c r="X187" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.55; 4H分金=26.60</t>
@@ -34236,7 +31584,6 @@
       <c r="V188" t="n">
         <v>126.6399993896484</v>
       </c>
-      <c r="W188" t="inlineStr"/>
       <c r="X188" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=126.64; Gann0=102.40; 段涨幅=23.67%</t>
@@ -34324,7 +31671,6 @@
       <c r="V189" t="n">
         <v>126.6399993896484</v>
       </c>
-      <c r="W189" t="inlineStr"/>
       <c r="X189" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.85; 4H分金=32.32</t>
@@ -34502,7 +31848,6 @@
       <c r="V191" t="n">
         <v>2060.080078125</v>
       </c>
-      <c r="W191" t="inlineStr"/>
       <c r="X191" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.18; 4H分金=51.85</t>
@@ -34590,7 +31935,6 @@
       <c r="V192" t="n">
         <v>188.1999969482422</v>
       </c>
-      <c r="W192" t="inlineStr"/>
       <c r="X192" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.91; 4H分金=49.93</t>
@@ -34768,7 +32112,6 @@
       <c r="V194" t="n">
         <v>143.0800018310547</v>
       </c>
-      <c r="W194" t="inlineStr"/>
       <c r="X194" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=143.08; Gann0=121.22; 段涨幅=18.03%</t>
@@ -34856,7 +32199,6 @@
       <c r="V195" t="n">
         <v>143.0800018310547</v>
       </c>
-      <c r="W195" t="inlineStr"/>
       <c r="X195" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.56; 4H分金=35.42</t>
@@ -34938,8 +32280,6 @@
       <c r="T196" t="b">
         <v>0</v>
       </c>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
       <c r="W196" t="n">
         <v>88</v>
       </c>
@@ -35030,7 +32370,6 @@
       <c r="V197" t="n">
         <v>33.81999969482422</v>
       </c>
-      <c r="W197" t="inlineStr"/>
       <c r="X197" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.55; 4H分金=43.70</t>
@@ -35118,7 +32457,6 @@
       <c r="V198" t="n">
         <v>73.29000091552734</v>
       </c>
-      <c r="W198" t="inlineStr"/>
       <c r="X198" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.01; 4H分金=47.34</t>
@@ -35296,7 +32634,6 @@
       <c r="V200" t="n">
         <v>406.6499938964844</v>
       </c>
-      <c r="W200" t="inlineStr"/>
       <c r="X200" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.90; 4H分金=55.39</t>
@@ -35384,7 +32721,6 @@
       <c r="V201" t="n">
         <v>302.8599853515625</v>
       </c>
-      <c r="W201" t="inlineStr"/>
       <c r="X201" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=302.86; Gann0=200.89; 段涨幅=50.76%</t>
@@ -35556,9 +32892,6 @@
       <c r="T203" t="b">
         <v>1</v>
       </c>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr"/>
-      <c r="W203" t="inlineStr"/>
       <c r="X203" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.00; 4H分金=48.44</t>
@@ -36006,7 +33339,6 @@
       <c r="V208" t="n">
         <v>315</v>
       </c>
-      <c r="W208" t="inlineStr"/>
       <c r="X208" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.44; 4H分金=38.99</t>
@@ -36364,7 +33696,6 @@
       <c r="V212" t="n">
         <v>274.75</v>
       </c>
-      <c r="W212" t="inlineStr"/>
       <c r="X212" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.87; 4H分金=29.59</t>
@@ -36632,7 +33963,6 @@
       <c r="V215" t="n">
         <v>133.8600006103516</v>
       </c>
-      <c r="W215" t="inlineStr"/>
       <c r="X215" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=133.86; Gann0=69.92; 段涨幅=91.45%</t>
@@ -36720,7 +34050,6 @@
       <c r="V216" t="n">
         <v>178.9100036621094</v>
       </c>
-      <c r="W216" t="inlineStr"/>
       <c r="X216" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=178.91; Gann0=147.57; 段涨幅=21.24%</t>
@@ -36802,8 +34131,6 @@
       <c r="T217" t="b">
         <v>0</v>
       </c>
-      <c r="U217" t="inlineStr"/>
-      <c r="V217" t="inlineStr"/>
       <c r="W217" t="n">
         <v>94</v>
       </c>
@@ -36894,7 +34221,6 @@
       <c r="V218" t="n">
         <v>68.97000122070312</v>
       </c>
-      <c r="W218" t="inlineStr"/>
       <c r="X218" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-18; 1出价格=68.97; Gann0=61.71; 段涨幅=11.76%</t>
@@ -36982,7 +34308,6 @@
       <c r="V219" t="n">
         <v>73.73999786376953</v>
       </c>
-      <c r="W219" t="inlineStr"/>
       <c r="X219" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.65; 4H分金=39.11</t>
@@ -37070,7 +34395,6 @@
       <c r="V220" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W220" t="inlineStr"/>
       <c r="X220" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=149.31; Gann0=122.00; 段涨幅=22.39%</t>
@@ -37158,7 +34482,6 @@
       <c r="V221" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W221" t="inlineStr"/>
       <c r="X221" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.17; 4H分金=37.91</t>
@@ -37240,8 +34563,6 @@
       <c r="T222" t="b">
         <v>0</v>
       </c>
-      <c r="U222" t="inlineStr"/>
-      <c r="V222" t="inlineStr"/>
       <c r="W222" t="n">
         <v>86</v>
       </c>
@@ -37422,7 +34743,6 @@
       <c r="V224" t="n">
         <v>409.6499938964844</v>
       </c>
-      <c r="W224" t="inlineStr"/>
       <c r="X224" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.92; 4H分金=50.49</t>
@@ -37908,7 +35228,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -38314,8 +35634,6 @@
       <c r="T234" t="b">
         <v>0</v>
       </c>
-      <c r="U234" t="inlineStr"/>
-      <c r="V234" t="inlineStr"/>
       <c r="W234" t="n">
         <v>91</v>
       </c>
@@ -38406,7 +35724,6 @@
       <c r="V235" t="n">
         <v>11.90999984741211</v>
       </c>
-      <c r="W235" t="inlineStr"/>
       <c r="X235" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.02; 4H分金=49.87</t>
@@ -38494,7 +35811,6 @@
       <c r="V236" t="n">
         <v>643</v>
       </c>
-      <c r="W236" t="inlineStr"/>
       <c r="X236" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=643.00; Gann0=594.81; 段涨幅=8.10%</t>
@@ -38582,7 +35898,6 @@
       <c r="V237" t="n">
         <v>643</v>
       </c>
-      <c r="W237" t="inlineStr"/>
       <c r="X237" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=40.60; 4H分金=32.16</t>
@@ -38670,7 +35985,6 @@
       <c r="V238" t="n">
         <v>24.5</v>
       </c>
-      <c r="W238" t="inlineStr"/>
       <c r="X238" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.29; 4H分金=49.04</t>
@@ -38758,7 +36072,6 @@
       <c r="V239" t="n">
         <v>134.1100006103516</v>
       </c>
-      <c r="W239" t="inlineStr"/>
       <c r="X239" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.14; 4H分金=41.50</t>
@@ -38840,8 +36153,6 @@
       <c r="T240" t="b">
         <v>0</v>
       </c>
-      <c r="U240" t="inlineStr"/>
-      <c r="V240" t="inlineStr"/>
       <c r="W240" t="n">
         <v>95</v>
       </c>
@@ -39112,7 +36423,6 @@
       <c r="V243" t="n">
         <v>33.81999969482422</v>
       </c>
-      <c r="W243" t="inlineStr"/>
       <c r="X243" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=33.82; Gann0=17.50; 段涨幅=93.26%</t>
@@ -39470,7 +36780,6 @@
       <c r="V247" t="n">
         <v>56.84000015258789</v>
       </c>
-      <c r="W247" t="inlineStr"/>
       <c r="X247" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.79; 4H分金=45.24</t>
@@ -39828,7 +37137,6 @@
       <c r="V251" t="n">
         <v>16.76000022888184</v>
       </c>
-      <c r="W251" t="inlineStr"/>
       <c r="X251" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.29; 4H分金=52.30</t>
@@ -39916,7 +37224,6 @@
       <c r="V252" t="n">
         <v>86.43000030517578</v>
       </c>
-      <c r="W252" t="inlineStr"/>
       <c r="X252" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.54; 4H分金=45.20</t>
@@ -40004,7 +37311,6 @@
       <c r="V253" t="n">
         <v>394.6300048828125</v>
       </c>
-      <c r="W253" t="inlineStr"/>
       <c r="X253" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.55; 4H分金=50.76</t>
@@ -40092,7 +37398,6 @@
       <c r="V254" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W254" t="inlineStr"/>
       <c r="X254" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=445.60; Gann0=393.63; 段涨幅=13.20%</t>
@@ -40180,7 +37485,6 @@
       <c r="V255" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W255" t="inlineStr"/>
       <c r="X255" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.10; 4H分金=24.03</t>
@@ -40268,7 +37572,6 @@
       <c r="V256" t="n">
         <v>13.93000030517578</v>
       </c>
-      <c r="W256" t="inlineStr"/>
       <c r="X256" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.48; 4H分金=47.96</t>
@@ -40350,8 +37653,6 @@
       <c r="T257" t="b">
         <v>0</v>
       </c>
-      <c r="U257" t="inlineStr"/>
-      <c r="V257" t="inlineStr"/>
       <c r="W257" t="n">
         <v>86</v>
       </c>
@@ -40436,8 +37737,6 @@
       <c r="T258" t="b">
         <v>0</v>
       </c>
-      <c r="U258" t="inlineStr"/>
-      <c r="V258" t="inlineStr"/>
       <c r="W258" t="n">
         <v>91</v>
       </c>
@@ -40528,7 +37827,6 @@
       <c r="V259" t="n">
         <v>167.3999938964844</v>
       </c>
-      <c r="W259" t="inlineStr"/>
       <c r="X259" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.12; 4H分金=40.44</t>
@@ -40616,7 +37914,6 @@
       <c r="V260" t="n">
         <v>51.58000183105469</v>
       </c>
-      <c r="W260" t="inlineStr"/>
       <c r="X260" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.41; 4H分金=45.41</t>
@@ -40955,7 +38252,6 @@
       <c r="D2" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46170</v>
       </c>
@@ -41004,7 +38300,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="8" t="n">
         <v>46164</v>
       </c>
@@ -41113,7 +38408,6 @@
       <c r="D5" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="8" t="n">
         <v>46164</v>
       </c>
@@ -41219,7 +38513,6 @@
       <c r="D7" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="8" t="n">
         <v>46170</v>
       </c>
@@ -41325,7 +38618,6 @@
       <c r="D9" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="8" t="n">
         <v>46164</v>
       </c>
@@ -41930,7 +39222,6 @@
       <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="8" t="n">
         <v>46171</v>
       </c>
@@ -42042,7 +39333,6 @@
       <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46169</v>
       </c>
@@ -42131,7 +39421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -42280,7 +39570,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -42660,7 +39949,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -43040,7 +40328,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -43168,7 +40455,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -43484,7 +40770,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -43548,7 +40833,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -43612,7 +40896,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -43670,7 +40953,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -43736,7 +41019,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -43767,7 +41049,6 @@
       <c r="Q26" s="19" t="n">
         <v>-0.023779</v>
       </c>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -43790,7 +41071,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -44046,7 +41327,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -44106,7 +41387,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -44401,9 +41682,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="21" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -44493,11 +41772,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44509,7 +41783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -44670,24 +41944,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -44739,24 +42001,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -44808,24 +42058,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -44877,24 +42115,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -44946,24 +42172,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45015,24 +42223,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45084,24 +42280,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45153,24 +42337,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45222,24 +42388,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45291,24 +42445,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45360,24 +42502,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45429,24 +42559,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45498,24 +42616,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45567,24 +42667,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45636,24 +42718,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45705,24 +42769,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45774,24 +42826,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45843,24 +42883,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -45912,24 +42934,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -46166,24 +43176,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -46228,11 +43226,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46244,7 +43237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -46665,7 +43658,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
@@ -46841,7 +43834,6 @@
       <c r="F11" t="n">
         <v>105.89</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>104.27</v>
       </c>
@@ -47218,7 +44210,6 @@
       <c r="O17" s="19" t="n">
         <v>-0.007566</v>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -47809,7 +44800,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -47844,7 +44835,6 @@
       <c r="O28" s="11" t="n">
         <v>0.031388</v>
       </c>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -47867,7 +44857,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -47975,7 +44965,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -48198,9 +45188,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="21" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -48252,9 +45240,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="21" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -48306,9 +45292,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="21" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -48360,9 +45344,7 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="B46" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="21" t="n"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -48414,9 +45396,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B47" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="21" t="n"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -48468,9 +45448,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B48" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B48" s="21" t="n"/>
       <c r="C48" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -48522,9 +45500,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B49" s="21" t="n"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -48576,9 +45552,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B50" s="21" t="n"/>
       <c r="C50" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -48701,8 +45675,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
